--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
   <si>
     <t>Id</t>
   </si>
@@ -161,15 +161,27 @@
     <t>伤害减免</t>
   </si>
   <si>
+    <t>精炼等级</t>
+  </si>
+  <si>
     <t>精炼等级+5</t>
   </si>
   <si>
+    <t>宠物备战</t>
+  </si>
+  <si>
     <t>宠物备战位+1</t>
   </si>
   <si>
+    <t>宠物继承</t>
+  </si>
+  <si>
     <t>宠物继承损耗-5</t>
   </si>
   <si>
+    <t>强化等级</t>
+  </si>
+  <si>
     <t>强化等级+5</t>
   </si>
   <si>
@@ -179,16 +191,28 @@
     <t>经验增幅</t>
   </si>
   <si>
+    <t>技能出站</t>
+  </si>
+  <si>
     <t>技能出站位+1</t>
   </si>
   <si>
+    <t>技能词条</t>
+  </si>
+  <si>
     <t>技能词条需求-1</t>
   </si>
   <si>
     <t>宠物继承损耗-15</t>
   </si>
   <si>
+    <t>宠物出战</t>
+  </si>
+  <si>
     <t>宠物出战位置+1</t>
+  </si>
+  <si>
+    <t>免广</t>
   </si>
   <si>
     <t>免广并且收益翻倍</t>
@@ -824,10 +848,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1163,62 +1186,62 @@
   </cols>
   <sheetData>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1303,7 +1326,7 @@
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -1322,11 +1345,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C11" s="3">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C11" s="2">
         <v>6</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="1">
@@ -1338,15 +1361,15 @@
       <c r="G11" s="1">
         <v>3</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C12" s="3">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C12" s="2">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="1">
@@ -1355,18 +1378,18 @@
       <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>4</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C13" s="3">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C13" s="2">
         <v>8</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="1">
@@ -1375,18 +1398,18 @@
       <c r="F13" s="1">
         <v>1</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>4</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C14" s="3">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C14" s="2">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="1">
@@ -1395,15 +1418,15 @@
       <c r="F14" s="1">
         <v>1</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>4</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -1415,7 +1438,7 @@
       <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>4</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -1423,7 +1446,7 @@
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -1435,7 +1458,7 @@
       <c r="F16" s="1">
         <v>1</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>4</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -1443,7 +1466,7 @@
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -1455,7 +1478,7 @@
       <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>4</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -1463,16 +1486,19 @@
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>13</v>
       </c>
+      <c r="D18" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="E18" s="1">
         <v>1</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>4</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -1480,42 +1506,51 @@
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>14</v>
       </c>
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>4</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C20" s="3">
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C20" s="2">
         <v>15</v>
       </c>
+      <c r="D20" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="2">
         <v>4</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>16</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -1531,8 +1566,11 @@
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>17</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -1547,9 +1585,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C23" s="3">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C23" s="2">
         <v>18</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -1560,13 +1601,16 @@
       <c r="G23" s="2">
         <v>5</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <v>19</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -1582,8 +1626,11 @@
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C25" s="3">
+      <c r="C25" s="2">
         <v>20</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -1599,8 +1646,11 @@
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <v>21</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -1615,9 +1665,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C27" s="3">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C27" s="2">
         <v>22</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -1628,13 +1681,16 @@
       <c r="G27" s="2">
         <v>5</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C28" s="3">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C28" s="2">
         <v>23</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -1645,234 +1701,273 @@
       <c r="G28" s="2">
         <v>5</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C29" s="3">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C29" s="2">
         <v>24</v>
       </c>
+      <c r="D29" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
         <v>1</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="2">
         <v>6</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C30" s="3">
+      <c r="H29" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C30" s="2">
         <v>25</v>
       </c>
+      <c r="D30" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
         <v>1</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="2">
         <v>6</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C31" s="3">
+      <c r="H30" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C31" s="2">
         <v>26</v>
       </c>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
         <v>1</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="2">
         <v>6</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C32" s="3">
+      <c r="H31" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C32" s="2">
         <v>27</v>
       </c>
+      <c r="D32" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="2">
         <v>6</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C33" s="3">
+      <c r="H32" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C33" s="2">
         <v>28</v>
       </c>
+      <c r="D33" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="2">
         <v>6</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C34" s="2">
+        <v>29</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>6</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C35" s="2">
+        <v>30</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2">
+        <v>6</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C36" s="2">
+        <v>31</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2">
+        <v>6</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C37" s="2">
+        <v>32</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2">
+        <v>7</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C38" s="2">
+        <v>33</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2">
+        <v>7</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C39" s="2">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="34" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C34" s="3">
-        <v>29</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3">
-        <v>6</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C35" s="3">
-        <v>30</v>
-      </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3">
-        <v>6</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C36" s="3">
-        <v>31</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1</v>
-      </c>
-      <c r="G36" s="3">
-        <v>6</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C37" s="3">
-        <v>32</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3">
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
         <v>7</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C38" s="3">
-        <v>33</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="H39" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C40" s="2">
+        <v>35</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2">
         <v>7</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C39" s="3">
-        <v>34</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3">
+      <c r="H40" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="2">
+        <v>36</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2">
         <v>7</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C40" s="3">
-        <v>35</v>
-      </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="1">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3">
-        <v>7</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" s="3" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C41" s="3">
-        <v>36</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3">
-        <v>7</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>54</v>
+      <c r="H41" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3:E3 C4 D4 E4 C5 D5:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="85">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
@@ -41,6 +44,12 @@
     <t>AtrVueList</t>
   </si>
   <si>
+    <t>SpeId</t>
+  </si>
+  <si>
+    <t>SpeVue</t>
+  </si>
+  <si>
     <t>Quality</t>
   </si>
   <si>
@@ -56,166 +65,223 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>小药囊</t>
+  </si>
+  <si>
+    <t>血量加成</t>
+  </si>
+  <si>
+    <t>小铁盾</t>
+  </si>
+  <si>
+    <t>防御加成</t>
+  </si>
+  <si>
+    <t>小铁剑</t>
+  </si>
+  <si>
+    <t>攻击加成</t>
+  </si>
+  <si>
     <t>小木剑</t>
   </si>
   <si>
-    <t>物攻</t>
+    <t>物攻加成</t>
   </si>
   <si>
     <t>小珍珠</t>
   </si>
   <si>
-    <t>法攻</t>
+    <t>法攻加成</t>
   </si>
   <si>
     <t>小罗盘</t>
   </si>
   <si>
-    <t>道攻</t>
-  </si>
-  <si>
-    <t>小铁剑</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>小铁盾</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>小药囊</t>
-  </si>
-  <si>
-    <t>血量</t>
-  </si>
-  <si>
-    <t>青铜剑</t>
-  </si>
-  <si>
-    <t>物攻加成</t>
-  </si>
-  <si>
-    <t>乌木剑</t>
-  </si>
-  <si>
-    <t>魔法加成</t>
-  </si>
-  <si>
-    <t>桃木剑</t>
-  </si>
-  <si>
-    <t>道术加成</t>
-  </si>
-  <si>
-    <t>金戒指</t>
-  </si>
-  <si>
-    <t>攻击加成</t>
-  </si>
-  <si>
-    <t>金手镯</t>
-  </si>
-  <si>
-    <t>防御加成</t>
-  </si>
-  <si>
-    <t>金项链</t>
-  </si>
-  <si>
-    <t>生命加成</t>
+    <t>道攻加成</t>
+  </si>
+  <si>
+    <t>大药囊</t>
+  </si>
+  <si>
+    <t>大铁盾</t>
+  </si>
+  <si>
+    <t>大铁剑</t>
+  </si>
+  <si>
+    <t>大木剑</t>
+  </si>
+  <si>
+    <t>大珍珠</t>
+  </si>
+  <si>
+    <t>大罗盘</t>
+  </si>
+  <si>
+    <t>蛮力戒指</t>
   </si>
   <si>
     <t>物伤加成</t>
   </si>
   <si>
+    <t>魔力戒指</t>
+  </si>
+  <si>
     <t>法伤加成</t>
   </si>
   <si>
+    <t>神力戒指</t>
+  </si>
+  <si>
     <t>道伤加成</t>
   </si>
   <si>
+    <t>银沙挂坠</t>
+  </si>
+  <si>
+    <t>血量增幅</t>
+  </si>
+  <si>
+    <t>回光护手</t>
+  </si>
+  <si>
+    <t>防御增幅</t>
+  </si>
+  <si>
+    <t>流风长剑</t>
+  </si>
+  <si>
+    <t>攻击增幅</t>
+  </si>
+  <si>
+    <t>暴击护符</t>
+  </si>
+  <si>
     <t>暴击</t>
   </si>
   <si>
+    <t>爆伤护符</t>
+  </si>
+  <si>
     <t>爆伤</t>
   </si>
   <si>
+    <t>弱点护符</t>
+  </si>
+  <si>
     <t>致命</t>
   </si>
   <si>
+    <t>致命护符</t>
+  </si>
+  <si>
     <t>致命伤害</t>
   </si>
   <si>
+    <t>攻速护符</t>
+  </si>
+  <si>
     <t>攻速</t>
   </si>
   <si>
+    <t>冷却护符</t>
+  </si>
+  <si>
     <t>冷却</t>
   </si>
   <si>
+    <t>伤害护符</t>
+  </si>
+  <si>
     <t>伤害加成</t>
   </si>
   <si>
+    <t>免伤护符</t>
+  </si>
+  <si>
     <t>伤害减免</t>
   </si>
   <si>
-    <t>精炼等级</t>
-  </si>
-  <si>
-    <t>精炼等级+5</t>
-  </si>
-  <si>
-    <t>宠物备战</t>
+    <t>铁匠锤</t>
+  </si>
+  <si>
+    <t>2001,2002,2003</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>精炼等级上限+5</t>
+  </si>
+  <si>
+    <t>6开始，固定属性为攻击，防御，血量增幅为5%</t>
+  </si>
+  <si>
+    <t>魔法书</t>
+  </si>
+  <si>
+    <t>技能出站位+1</t>
+  </si>
+  <si>
+    <t>7开始，固定属性为攻击，防御，血量倍率为3%</t>
+  </si>
+  <si>
+    <t>秘之契约</t>
+  </si>
+  <si>
+    <t>宠物继承损耗-5</t>
+  </si>
+  <si>
+    <t>学徒铁锤</t>
+  </si>
+  <si>
+    <t>强化等级上限+5</t>
+  </si>
+  <si>
+    <t>神鹰之翼</t>
+  </si>
+  <si>
+    <t>急速匕首</t>
+  </si>
+  <si>
+    <t>痛苦荆棘</t>
+  </si>
+  <si>
+    <t>影魔之刃</t>
+  </si>
+  <si>
+    <t>技能印记</t>
+  </si>
+  <si>
+    <t>10001,10002,10003</t>
+  </si>
+  <si>
+    <t>技能词条需求-1</t>
+  </si>
+  <si>
+    <t>神之契约</t>
+  </si>
+  <si>
+    <t>宠物继承损耗-15</t>
+  </si>
+  <si>
+    <t>黄金兽栏</t>
   </si>
   <si>
     <t>宠物备战位+1</t>
   </si>
   <si>
-    <t>宠物继承</t>
-  </si>
-  <si>
-    <t>宠物继承损耗-5</t>
-  </si>
-  <si>
-    <t>强化等级</t>
-  </si>
-  <si>
-    <t>强化等级+5</t>
-  </si>
-  <si>
-    <t>金币增幅</t>
-  </si>
-  <si>
-    <t>经验增幅</t>
-  </si>
-  <si>
-    <t>技能出站</t>
-  </si>
-  <si>
-    <t>技能出站位+1</t>
-  </si>
-  <si>
-    <t>技能词条</t>
-  </si>
-  <si>
-    <t>技能词条需求-1</t>
-  </si>
-  <si>
-    <t>宠物继承损耗-15</t>
-  </si>
-  <si>
-    <t>宠物出战</t>
+    <t>驯兽金印</t>
   </si>
   <si>
     <t>宠物出战位置+1</t>
   </si>
   <si>
-    <t>免广</t>
-  </si>
-  <si>
-    <t>免广并且收益翻倍</t>
+    <t>传奇铁锤</t>
+  </si>
+  <si>
+    <t>装备基础属性+50%</t>
   </si>
 </sst>
 </file>
@@ -228,7 +294,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +312,12 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -718,143 +790,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1174,795 +1252,1163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:H41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="C1:L48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="12.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="6" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="43" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="1" customHeight="1" spans="3:12">
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:12">
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:12">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="K6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:12">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>3</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:12">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>3</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:12">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>3</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>3</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>3</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C13" s="1">
+        <v>2001</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1001</v>
+      </c>
+      <c r="F13" s="1">
+        <v>15</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
         <v>4</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:8">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:8">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>3</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:8">
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="K13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>3</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:8">
-      <c r="C9" s="1">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>3</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>3</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C11" s="2">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>3</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C12" s="2">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
-        <v>4</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C13" s="2">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>4</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C14" s="2">
-        <v>9</v>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C14" s="1">
+        <v>2002</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="1">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
         <v>4</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="K14" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C15" s="1">
+        <v>2003</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C15" s="2">
+      <c r="E15" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F15" s="1">
+        <v>15</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>4</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C16" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1004</v>
+      </c>
+      <c r="F16" s="1">
+        <v>15</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>4</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C17" s="1">
+        <v>2005</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1005</v>
+      </c>
+      <c r="F17" s="1">
+        <v>15</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C18" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1006</v>
+      </c>
+      <c r="F18" s="1">
+        <v>15</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>4</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C19" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1007</v>
+      </c>
+      <c r="F19" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2">
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
         <v>4</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C16" s="2">
-        <v>11</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
+      <c r="K19" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C20" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1008</v>
+      </c>
+      <c r="F20" s="1">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
         <v>4</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C17" s="2">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
+      <c r="K20" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C21" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1009</v>
+      </c>
+      <c r="F21" s="1">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
         <v>4</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C18" s="2">
-        <v>13</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2">
-        <v>4</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C19" s="2">
-        <v>14</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2">
-        <v>4</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C20" s="2">
-        <v>15</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C21" s="2">
-        <v>16</v>
-      </c>
-      <c r="D21" s="2" t="s">
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C22" s="1">
+        <v>2010</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2">
-        <v>5</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C22" s="2">
-        <v>17</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E22" s="1">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
       </c>
-      <c r="G22" s="2">
-        <v>5</v>
-      </c>
-      <c r="H22" s="2" t="s">
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>4</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C23" s="2">
-        <v>18</v>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C23" s="1">
+        <v>2011</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E23" s="1">
-        <v>1</v>
+        <v>2002</v>
       </c>
       <c r="F23" s="1">
         <v>1</v>
       </c>
-      <c r="G23" s="2">
-        <v>5</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C24" s="2">
-        <v>19</v>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>4</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C24" s="1">
+        <v>2012</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" s="1">
-        <v>1</v>
+        <v>2003</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>4</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C26" s="1">
+        <v>3001</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="1">
+        <v>21</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
         <v>5</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C25" s="2">
+      <c r="K26" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C27" s="1">
+        <v>3002</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="1">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>5</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C28" s="1">
+        <v>3003</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="1">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>5</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C29" s="1">
+        <v>3004</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="1">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1">
+        <v>20</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>5</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C30" s="1">
+        <v>3005</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="1">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1">
+        <v>3</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C31" s="1">
+        <v>3006</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="1">
+        <v>10</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>5</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C32" s="1">
+        <v>3007</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="1">
+        <v>27</v>
+      </c>
+      <c r="F32" s="1">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>5</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C33" s="1">
+        <v>3008</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="1">
+        <v>28</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C35" s="1">
+        <v>4001</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="1">
+        <v>116</v>
+      </c>
+      <c r="H35" s="1">
+        <v>5</v>
+      </c>
+      <c r="I35" s="2">
+        <v>6</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C36" s="1">
+        <v>4002</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36" s="1">
+        <v>113</v>
+      </c>
+      <c r="H36" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="1">
+      <c r="I36" s="2">
+        <v>6</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C37" s="1">
+        <v>4003</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G37" s="1">
+        <v>115</v>
+      </c>
+      <c r="H37" s="1">
+        <v>5</v>
+      </c>
+      <c r="I37" s="2">
+        <v>6</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C38" s="1">
+        <v>4004</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="1">
+        <v>117</v>
+      </c>
+      <c r="H38" s="1">
+        <v>5</v>
+      </c>
+      <c r="I38" s="2">
+        <v>6</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
+        <v>4005</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="1">
+        <v>11</v>
+      </c>
+      <c r="H39" s="1">
+        <v>10</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C40" s="1">
+        <v>4006</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40" s="1">
+        <v>10</v>
+      </c>
+      <c r="H40" s="1">
+        <v>10</v>
+      </c>
+      <c r="I40" s="2">
+        <v>6</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C41" s="1">
+        <v>4007</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="1">
+        <v>21</v>
+      </c>
+      <c r="H41" s="1">
+        <v>5</v>
+      </c>
+      <c r="I41" s="2">
+        <v>6</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C42" s="1">
+        <v>4008</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="1">
+        <v>22</v>
+      </c>
+      <c r="H42" s="1">
+        <v>25</v>
+      </c>
+      <c r="I42" s="2">
+        <v>6</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C43" s="1"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C44" s="1">
+        <v>5001</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="1">
+        <v>114</v>
+      </c>
+      <c r="H44" s="1">
         <v>1</v>
       </c>
-      <c r="G25" s="2">
-        <v>5</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C26" s="2">
-        <v>21</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="I44" s="2">
+        <v>7</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C45" s="1">
+        <v>5002</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="1">
+        <v>115</v>
+      </c>
+      <c r="H45" s="1">
+        <v>15</v>
+      </c>
+      <c r="I45" s="2">
+        <v>7</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C46" s="1">
+        <v>5003</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="1">
+        <v>111</v>
+      </c>
+      <c r="H46" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="1">
+      <c r="I46" s="2">
+        <v>7</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C47" s="1">
+        <v>5004</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G47" s="2">
+        <v>112</v>
+      </c>
+      <c r="H47" s="1">
         <v>1</v>
       </c>
-      <c r="G26" s="2">
-        <v>5</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C27" s="2">
-        <v>22</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2">
-        <v>5</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C28" s="2">
-        <v>23</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2">
-        <v>5</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C29" s="2">
-        <v>24</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2">
-        <v>6</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C30" s="2">
-        <v>25</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2">
-        <v>6</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C31" s="2">
-        <v>26</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2">
-        <v>6</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C32" s="2">
-        <v>27</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="I47" s="2">
+        <v>7</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C48" s="1">
+        <v>5005</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G48" s="1">
+        <v>20001</v>
+      </c>
+      <c r="H48" s="1">
         <v>50</v>
       </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2">
-        <v>6</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C33" s="2">
-        <v>28</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2">
-        <v>6</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C34" s="2">
-        <v>29</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2">
-        <v>6</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C35" s="2">
-        <v>30</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2">
-        <v>6</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C36" s="2">
-        <v>31</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2">
-        <v>6</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C37" s="2">
-        <v>32</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2">
+      <c r="I48" s="2">
         <v>7</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C38" s="2">
-        <v>33</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2">
-        <v>7</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C39" s="2">
-        <v>34</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1</v>
-      </c>
-      <c r="G39" s="2">
-        <v>7</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C40" s="2">
-        <v>35</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="1">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2">
-        <v>7</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C41" s="2">
-        <v>36</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
-      <c r="G41" s="2">
-        <v>7</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>62</v>
+      <c r="K48" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="87">
   <si>
     <t>#</t>
   </si>
@@ -50,7 +50,13 @@
     <t>SpeVue</t>
   </si>
   <si>
+    <t>SpeLevel</t>
+  </si>
+  <si>
     <t>Quality</t>
+  </si>
+  <si>
+    <t>Max</t>
   </si>
   <si>
     <t>Des</t>
@@ -1252,37 +1258,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L48"/>
+  <dimension ref="C1:N48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="6" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="43" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="6" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="11" width="11.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="39.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:12">
-      <c r="K1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:12">
-      <c r="K2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="1" customHeight="1" spans="3:14">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:14">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1307,8 +1313,14 @@
       <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1333,39 +1345,51 @@
       <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:12">
+        <v>11</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:14">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1">
         <v>1001</v>
@@ -1380,18 +1404,24 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>3</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:12">
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:14">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1">
         <v>1002</v>
@@ -1406,18 +1436,24 @@
         <v>0</v>
       </c>
       <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
         <v>3</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:12">
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <v>1003</v>
@@ -1432,18 +1468,24 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
         <v>3</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:12">
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:14">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1">
         <v>1004</v>
@@ -1458,18 +1500,24 @@
         <v>0</v>
       </c>
       <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
         <v>3</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1">
         <v>1005</v>
@@ -1484,18 +1532,24 @@
         <v>0</v>
       </c>
       <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
         <v>3</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E11" s="1">
         <v>1006</v>
@@ -1510,13 +1564,19 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
         <v>3</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1524,14 +1584,16 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C13" s="1">
         <v>2001</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1">
         <v>1001</v>
@@ -1545,19 +1607,25 @@
       <c r="H13" s="1">
         <v>0</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
         <v>4</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C14" s="1">
         <v>2002</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1">
         <v>1002</v>
@@ -1571,19 +1639,25 @@
       <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
         <v>4</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C15" s="1">
         <v>2003</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" s="1">
         <v>1003</v>
@@ -1597,19 +1671,25 @@
       <c r="H15" s="1">
         <v>0</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
         <v>4</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="1">
         <v>2004</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1">
         <v>1004</v>
@@ -1623,19 +1703,25 @@
       <c r="H16" s="1">
         <v>0</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
         <v>4</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C17" s="1">
         <v>2005</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1">
         <v>1005</v>
@@ -1649,19 +1735,25 @@
       <c r="H17" s="1">
         <v>0</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
         <v>4</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C18" s="1">
         <v>2006</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1">
         <v>1006</v>
@@ -1675,19 +1767,25 @@
       <c r="H18" s="1">
         <v>0</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
         <v>4</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C19" s="1">
         <v>2007</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E19" s="1">
         <v>1007</v>
@@ -1701,19 +1799,25 @@
       <c r="H19" s="1">
         <v>0</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
         <v>4</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C20" s="1">
         <v>2008</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" s="1">
         <v>1008</v>
@@ -1727,19 +1831,25 @@
       <c r="H20" s="1">
         <v>0</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
         <v>4</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="1">
         <v>2009</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" s="1">
         <v>1009</v>
@@ -1753,19 +1863,25 @@
       <c r="H21" s="1">
         <v>0</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
         <v>4</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C22" s="1">
         <v>2010</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E22" s="1">
         <v>2001</v>
@@ -1779,19 +1895,25 @@
       <c r="H22" s="1">
         <v>0</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="J22" s="2">
         <v>4</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K22" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="1">
         <v>2011</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E23" s="1">
         <v>2002</v>
@@ -1805,19 +1927,25 @@
       <c r="H23" s="1">
         <v>0</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="1">
+        <v>10</v>
+      </c>
+      <c r="J23" s="2">
         <v>4</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K23" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C24" s="1">
         <v>2012</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E24" s="1">
         <v>2003</v>
@@ -1831,26 +1959,33 @@
       <c r="H24" s="1">
         <v>0</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="1">
+        <v>10</v>
+      </c>
+      <c r="J24" s="2">
         <v>4</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K24" s="1">
+        <v>9999</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C26" s="1">
         <v>3001</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E26" s="1">
         <v>21</v>
@@ -1864,19 +1999,25 @@
       <c r="H26" s="1">
         <v>0</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
         <v>5</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="1">
         <v>3002</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E27" s="1">
         <v>22</v>
@@ -1890,19 +2031,25 @@
       <c r="H27" s="1">
         <v>0</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
         <v>5</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="1">
         <v>3003</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E28" s="1">
         <v>23</v>
@@ -1916,19 +2063,25 @@
       <c r="H28" s="1">
         <v>0</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
         <v>5</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C29" s="1">
         <v>3004</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E29" s="1">
         <v>24</v>
@@ -1942,19 +2095,25 @@
       <c r="H29" s="1">
         <v>0</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
         <v>5</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="1">
         <v>3005</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E30" s="1">
         <v>11</v>
@@ -1968,19 +2127,25 @@
       <c r="H30" s="1">
         <v>0</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
         <v>5</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="1">
         <v>3006</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E31" s="1">
         <v>10</v>
@@ -1994,19 +2159,25 @@
       <c r="H31" s="1">
         <v>0</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
         <v>5</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="1">
         <v>3007</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E32" s="1">
         <v>27</v>
@@ -2020,19 +2191,25 @@
       <c r="H32" s="1">
         <v>0</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
         <v>5</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C33" s="1">
         <v>3008</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E33" s="1">
         <v>28</v>
@@ -2046,32 +2223,39 @@
       <c r="H33" s="1">
         <v>0</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
         <v>5</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C35" s="1">
         <v>4001</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G35" s="1">
         <v>116</v>
@@ -2079,28 +2263,34 @@
       <c r="H35" s="1">
         <v>5</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
         <v>6</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C36" s="1">
         <v>4002</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G36" s="1">
         <v>113</v>
@@ -2108,28 +2298,34 @@
       <c r="H36" s="1">
         <v>1</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
         <v>6</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C37" s="1">
         <v>4003</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G37" s="1">
         <v>115</v>
@@ -2137,25 +2333,31 @@
       <c r="H37" s="1">
         <v>5</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2">
         <v>6</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C38" s="1">
         <v>4004</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G38" s="1">
         <v>117</v>
@@ -2163,25 +2365,31 @@
       <c r="H38" s="1">
         <v>5</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2">
         <v>6</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C39" s="1">
         <v>4005</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G39" s="1">
         <v>11</v>
@@ -2189,25 +2397,31 @@
       <c r="H39" s="1">
         <v>10</v>
       </c>
-      <c r="I39" s="2">
+      <c r="I39" s="1">
+        <v>1</v>
+      </c>
+      <c r="J39" s="2">
         <v>6</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C40" s="1">
         <v>4006</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G40" s="1">
         <v>10</v>
@@ -2215,25 +2429,31 @@
       <c r="H40" s="1">
         <v>10</v>
       </c>
-      <c r="I40" s="2">
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2">
         <v>6</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C41" s="1">
         <v>4007</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G41" s="1">
         <v>21</v>
@@ -2241,25 +2461,31 @@
       <c r="H41" s="1">
         <v>5</v>
       </c>
-      <c r="I41" s="2">
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2">
         <v>6</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K41" s="1">
+        <v>1</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C42" s="1">
         <v>4008</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G42" s="1">
         <v>22</v>
@@ -2267,32 +2493,39 @@
       <c r="H42" s="1">
         <v>25</v>
       </c>
-      <c r="I42" s="2">
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2">
         <v>6</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C43" s="1"/>
       <c r="E43" s="4"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C44" s="1">
         <v>5001</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G44" s="1">
         <v>114</v>
@@ -2300,25 +2533,31 @@
       <c r="H44" s="1">
         <v>1</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2">
         <v>7</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K44" s="1">
+        <v>1</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C45" s="1">
         <v>5002</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="F45" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G45" s="1">
         <v>115</v>
@@ -2326,25 +2565,31 @@
       <c r="H45" s="1">
         <v>15</v>
       </c>
-      <c r="I45" s="2">
+      <c r="I45" s="1">
+        <v>1</v>
+      </c>
+      <c r="J45" s="2">
         <v>7</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C46" s="1">
         <v>5003</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G46" s="1">
         <v>111</v>
@@ -2352,25 +2597,31 @@
       <c r="H46" s="1">
         <v>1</v>
       </c>
-      <c r="I46" s="2">
+      <c r="I46" s="1">
+        <v>1</v>
+      </c>
+      <c r="J46" s="2">
         <v>7</v>
       </c>
-      <c r="K46" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C47" s="1">
         <v>5004</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G47" s="2">
         <v>112</v>
@@ -2378,25 +2629,31 @@
       <c r="H47" s="1">
         <v>1</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I47" s="1">
+        <v>1</v>
+      </c>
+      <c r="J47" s="2">
         <v>7</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K47" s="1">
+        <v>1</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C48" s="1">
         <v>5005</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G48" s="1">
         <v>20001</v>
@@ -2404,11 +2661,17 @@
       <c r="H48" s="1">
         <v>50</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="1">
+        <v>1</v>
+      </c>
+      <c r="J48" s="2">
         <v>7</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>84</v>
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="120">
   <si>
     <t>#</t>
   </si>
@@ -59,6 +59,9 @@
     <t>Max</t>
   </si>
   <si>
+    <t>Fee</t>
+  </si>
+  <si>
     <t>Des</t>
   </si>
   <si>
@@ -74,51 +77,87 @@
     <t>小药囊</t>
   </si>
   <si>
+    <t>1,1001</t>
+  </si>
+  <si>
+    <t>2000,5</t>
+  </si>
+  <si>
     <t>血量加成</t>
   </si>
   <si>
     <t>小铁盾</t>
   </si>
   <si>
+    <t>2,1002</t>
+  </si>
+  <si>
+    <t>100,5</t>
+  </si>
+  <si>
     <t>防御加成</t>
   </si>
   <si>
     <t>小铁剑</t>
   </si>
   <si>
+    <t>3,1003</t>
+  </si>
+  <si>
     <t>攻击加成</t>
   </si>
   <si>
     <t>小木剑</t>
   </si>
   <si>
+    <t>4,1004</t>
+  </si>
+  <si>
+    <t>200,5</t>
+  </si>
+  <si>
     <t>物攻加成</t>
   </si>
   <si>
     <t>小珍珠</t>
   </si>
   <si>
+    <t>5,1005</t>
+  </si>
+  <si>
     <t>法攻加成</t>
   </si>
   <si>
     <t>小罗盘</t>
   </si>
   <si>
+    <t>6,1006</t>
+  </si>
+  <si>
     <t>道攻加成</t>
   </si>
   <si>
     <t>大药囊</t>
   </si>
   <si>
+    <t>10000,15</t>
+  </si>
+  <si>
     <t>大铁盾</t>
   </si>
   <si>
+    <t>500,15</t>
+  </si>
+  <si>
     <t>大铁剑</t>
   </si>
   <si>
     <t>大木剑</t>
   </si>
   <si>
+    <t>1000,15</t>
+  </si>
+  <si>
     <t>大珍珠</t>
   </si>
   <si>
@@ -128,82 +167,142 @@
     <t>蛮力戒指</t>
   </si>
   <si>
+    <t>4,1007</t>
+  </si>
+  <si>
+    <t>1000,10</t>
+  </si>
+  <si>
     <t>物伤加成</t>
   </si>
   <si>
     <t>魔力戒指</t>
   </si>
   <si>
+    <t>5,1008</t>
+  </si>
+  <si>
     <t>法伤加成</t>
   </si>
   <si>
     <t>神力戒指</t>
   </si>
   <si>
+    <t>5,1009</t>
+  </si>
+  <si>
     <t>道伤加成</t>
   </si>
   <si>
     <t>银沙挂坠</t>
   </si>
   <si>
+    <t>1001,2001</t>
+  </si>
+  <si>
+    <t>5,2</t>
+  </si>
+  <si>
     <t>血量增幅</t>
   </si>
   <si>
     <t>回光护手</t>
   </si>
   <si>
+    <t>1002,2002</t>
+  </si>
+  <si>
     <t>防御增幅</t>
   </si>
   <si>
     <t>流风长剑</t>
   </si>
   <si>
+    <t>1003,2003</t>
+  </si>
+  <si>
     <t>攻击增幅</t>
   </si>
   <si>
     <t>暴击护符</t>
   </si>
   <si>
+    <t>1001,21</t>
+  </si>
+  <si>
+    <t>20,3</t>
+  </si>
+  <si>
     <t>暴击</t>
   </si>
   <si>
     <t>爆伤护符</t>
   </si>
   <si>
+    <t>1002,22</t>
+  </si>
+  <si>
+    <t>10,20</t>
+  </si>
+  <si>
     <t>爆伤</t>
   </si>
   <si>
     <t>弱点护符</t>
   </si>
   <si>
+    <t>1003,23</t>
+  </si>
+  <si>
+    <t>10,3</t>
+  </si>
+  <si>
     <t>致命</t>
   </si>
   <si>
     <t>致命护符</t>
   </si>
   <si>
+    <t>1004,24</t>
+  </si>
+  <si>
     <t>致命伤害</t>
   </si>
   <si>
     <t>攻速护符</t>
   </si>
   <si>
+    <t>1005,11</t>
+  </si>
+  <si>
     <t>攻速</t>
   </si>
   <si>
     <t>冷却护符</t>
   </si>
   <si>
+    <t>1006,10</t>
+  </si>
+  <si>
     <t>冷却</t>
   </si>
   <si>
     <t>伤害护符</t>
   </si>
   <si>
+    <t>1007,27</t>
+  </si>
+  <si>
+    <t>10,10</t>
+  </si>
+  <si>
     <t>伤害加成</t>
   </si>
   <si>
     <t>免伤护符</t>
+  </si>
+  <si>
+    <t>1008,28</t>
   </si>
   <si>
     <t>伤害减免</t>
@@ -937,8 +1036,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1258,37 +1357,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N48"/>
+  <dimension ref="C1:O48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="6" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="11" width="11.125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="39.25" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="10" max="12" width="11.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="39.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="43" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:14">
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customHeight="1" spans="3:15">
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:14">
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:15">
       <c r="N2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1319,8 +1418,11 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1351,51 +1453,57 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:14">
+      <c r="M5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:15">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1001</v>
-      </c>
-      <c r="F6" s="1">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1412,22 +1520,25 @@
       <c r="K6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:14">
+      <c r="L6" s="1">
+        <v>88</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:15">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1002</v>
-      </c>
-      <c r="F7" s="1">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1444,22 +1555,25 @@
       <c r="K7" s="1">
         <v>1</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:14">
+      <c r="L7" s="1">
+        <v>88</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1003</v>
-      </c>
-      <c r="F8" s="1">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1476,22 +1590,25 @@
       <c r="K8" s="1">
         <v>1</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:14">
+      <c r="L8" s="1">
+        <v>88</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1004</v>
-      </c>
-      <c r="F9" s="1">
-        <v>5</v>
+        <v>26</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1508,22 +1625,25 @@
       <c r="K9" s="1">
         <v>1</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L9" s="1">
+        <v>88</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1005</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5</v>
+        <v>30</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1540,22 +1660,25 @@
       <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L10" s="1">
+        <v>88</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1006</v>
-      </c>
-      <c r="F11" s="1">
-        <v>5</v>
+        <v>33</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1572,11 +1695,14 @@
       <c r="K11" s="1">
         <v>1</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L11" s="1">
+        <v>88</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1586,20 +1712,21 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L12" s="1"/>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="1">
         <v>2001</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1001</v>
-      </c>
-      <c r="F13" s="1">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1616,22 +1743,25 @@
       <c r="K13" s="1">
         <v>1</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L13" s="1">
+        <v>188</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C14" s="1">
         <v>2002</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1002</v>
-      </c>
-      <c r="F14" s="1">
-        <v>15</v>
+        <v>38</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1648,22 +1778,25 @@
       <c r="K14" s="1">
         <v>1</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L14" s="1">
+        <v>188</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="1">
         <v>2003</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1003</v>
-      </c>
-      <c r="F15" s="1">
-        <v>15</v>
+        <v>40</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1680,22 +1813,25 @@
       <c r="K15" s="1">
         <v>1</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L15" s="1">
+        <v>188</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C16" s="1">
         <v>2004</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1004</v>
-      </c>
-      <c r="F16" s="1">
-        <v>15</v>
+        <v>41</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1712,22 +1848,25 @@
       <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L16" s="1">
+        <v>188</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C17" s="1">
         <v>2005</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1005</v>
-      </c>
-      <c r="F17" s="1">
-        <v>15</v>
+        <v>43</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1744,22 +1883,25 @@
       <c r="K17" s="1">
         <v>1</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L17" s="1">
+        <v>188</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C18" s="1">
         <v>2006</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1006</v>
-      </c>
-      <c r="F18" s="1">
-        <v>15</v>
+        <v>44</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1776,22 +1918,25 @@
       <c r="K18" s="1">
         <v>1</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L18" s="1">
+        <v>188</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C19" s="1">
         <v>2007</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1007</v>
-      </c>
-      <c r="F19" s="1">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -1808,22 +1953,25 @@
       <c r="K19" s="1">
         <v>1</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L19" s="1">
+        <v>188</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C20" s="1">
         <v>2008</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1008</v>
-      </c>
-      <c r="F20" s="1">
-        <v>10</v>
+        <v>49</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1840,22 +1988,25 @@
       <c r="K20" s="1">
         <v>1</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L20" s="1">
+        <v>188</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C21" s="1">
         <v>2009</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1009</v>
-      </c>
-      <c r="F21" s="1">
-        <v>10</v>
+        <v>52</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -1872,28 +2023,31 @@
       <c r="K21" s="1">
         <v>1</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L21" s="1">
+        <v>188</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C22" s="1">
         <v>2010</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="1">
-        <v>2001</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>10001</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="1">
         <v>10</v>
@@ -1904,28 +2058,31 @@
       <c r="K22" s="1">
         <v>9999</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L22" s="1">
+        <v>188</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C23" s="1">
         <v>2011</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="1">
-        <v>2002</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>10002</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="1">
         <v>10</v>
@@ -1936,28 +2093,31 @@
       <c r="K23" s="1">
         <v>9999</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L23" s="1">
+        <v>188</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="1">
         <v>2012</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2003</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>10003</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="1">
         <v>10</v>
@@ -1968,11 +2128,14 @@
       <c r="K24" s="1">
         <v>9999</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L24" s="1">
+        <v>188</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1980,18 +2143,18 @@
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="1">
         <v>3001</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="1">
-        <v>21</v>
-      </c>
-      <c r="F26" s="1">
-        <v>3</v>
+        <v>65</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -2008,22 +2171,25 @@
       <c r="K26" s="1">
         <v>1</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L26" s="1">
+        <v>588</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="1">
         <v>3002</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="1">
-        <v>22</v>
-      </c>
-      <c r="F27" s="1">
-        <v>20</v>
+        <v>69</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -2040,22 +2206,25 @@
       <c r="K27" s="1">
         <v>1</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L27" s="1">
+        <v>588</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C28" s="1">
         <v>3003</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="1">
-        <v>23</v>
-      </c>
-      <c r="F28" s="1">
-        <v>3</v>
+        <v>73</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -2072,22 +2241,25 @@
       <c r="K28" s="1">
         <v>1</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L28" s="1">
+        <v>588</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="1">
         <v>3004</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E29" s="1">
-        <v>24</v>
-      </c>
-      <c r="F29" s="1">
-        <v>20</v>
+        <v>77</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -2104,22 +2276,25 @@
       <c r="K29" s="1">
         <v>1</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L29" s="1">
+        <v>588</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="1">
         <v>3005</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E30" s="1">
-        <v>11</v>
-      </c>
-      <c r="F30" s="1">
-        <v>3</v>
+        <v>80</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -2136,22 +2311,25 @@
       <c r="K30" s="1">
         <v>1</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L30" s="1">
+        <v>588</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C31" s="1">
         <v>3006</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="1">
-        <v>10</v>
-      </c>
-      <c r="F31" s="1">
-        <v>3</v>
+        <v>83</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -2168,22 +2346,25 @@
       <c r="K31" s="1">
         <v>1</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L31" s="1">
+        <v>588</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C32" s="1">
         <v>3007</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="1">
-        <v>27</v>
-      </c>
-      <c r="F32" s="1">
-        <v>10</v>
+        <v>86</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -2200,22 +2381,25 @@
       <c r="K32" s="1">
         <v>1</v>
       </c>
-      <c r="M32" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L32" s="1">
+        <v>588</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C33" s="1">
         <v>3008</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33" s="1">
-        <v>28</v>
-      </c>
-      <c r="F33" s="1">
-        <v>10</v>
+        <v>90</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -2232,11 +2416,14 @@
       <c r="K33" s="1">
         <v>1</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L33" s="1">
+        <v>588</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -2244,18 +2431,18 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:14">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C35" s="1">
         <v>4001</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>62</v>
+        <v>93</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G35" s="1">
         <v>116</v>
@@ -2272,25 +2459,28 @@
       <c r="K35" s="1">
         <v>1</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L35" s="1">
+        <v>1888</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C36" s="1">
         <v>4002</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>62</v>
+        <v>98</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G36" s="1">
         <v>113</v>
@@ -2307,25 +2497,28 @@
       <c r="K36" s="1">
         <v>1</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>66</v>
+      <c r="L36" s="1">
+        <v>1888</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:14">
+        <v>99</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C37" s="1">
         <v>4003</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>62</v>
+        <v>101</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G37" s="1">
         <v>115</v>
@@ -2342,22 +2535,25 @@
       <c r="K37" s="1">
         <v>1</v>
       </c>
-      <c r="M37" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L37" s="1">
+        <v>1888</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C38" s="1">
         <v>4004</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>62</v>
+        <v>103</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G38" s="1">
         <v>117</v>
@@ -2374,22 +2570,25 @@
       <c r="K38" s="1">
         <v>1</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L38" s="1">
+        <v>1888</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C39" s="1">
         <v>4005</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>62</v>
+        <v>105</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G39" s="1">
         <v>11</v>
@@ -2406,22 +2605,25 @@
       <c r="K39" s="1">
         <v>1</v>
       </c>
-      <c r="M39" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L39" s="1">
+        <v>1888</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C40" s="1">
         <v>4006</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>62</v>
+        <v>106</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G40" s="1">
         <v>10</v>
@@ -2438,22 +2640,25 @@
       <c r="K40" s="1">
         <v>1</v>
       </c>
-      <c r="M40" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L40" s="1">
+        <v>1888</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C41" s="1">
         <v>4007</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>62</v>
+        <v>107</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G41" s="1">
         <v>21</v>
@@ -2470,22 +2675,25 @@
       <c r="K41" s="1">
         <v>1</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L41" s="1">
+        <v>1888</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C42" s="1">
         <v>4008</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>62</v>
+        <v>108</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G42" s="1">
         <v>22</v>
@@ -2502,11 +2710,14 @@
       <c r="K42" s="1">
         <v>1</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L42" s="1">
+        <v>1888</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C43" s="1"/>
       <c r="E43" s="4"/>
       <c r="F43" s="1"/>
@@ -2514,18 +2725,18 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:14">
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C44" s="1">
         <v>5001</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>62</v>
+        <v>109</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G44" s="1">
         <v>114</v>
@@ -2542,22 +2753,25 @@
       <c r="K44" s="1">
         <v>1</v>
       </c>
-      <c r="M44" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L44" s="1">
+        <v>4888</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C45" s="1">
         <v>5002</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>62</v>
+        <v>112</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G45" s="1">
         <v>115</v>
@@ -2574,22 +2788,25 @@
       <c r="K45" s="1">
         <v>1</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L45" s="1">
+        <v>4888</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C46" s="1">
         <v>5003</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>62</v>
+        <v>114</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G46" s="1">
         <v>111</v>
@@ -2606,22 +2823,25 @@
       <c r="K46" s="1">
         <v>1</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L46" s="1">
+        <v>4888</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C47" s="1">
         <v>5004</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>62</v>
+        <v>116</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G47" s="2">
         <v>112</v>
@@ -2638,22 +2858,25 @@
       <c r="K47" s="1">
         <v>1</v>
       </c>
-      <c r="M47" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L47" s="1">
+        <v>4888</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C48" s="1">
         <v>5005</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>62</v>
+        <v>118</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="G48" s="1">
         <v>20001</v>
@@ -2670,8 +2893,11 @@
       <c r="K48" s="1">
         <v>1</v>
       </c>
-      <c r="M48" s="2" t="s">
-        <v>86</v>
+      <c r="L48" s="1">
+        <v>4888</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -200,7 +200,7 @@
     <t>1001,2001</t>
   </si>
   <si>
-    <t>5,2</t>
+    <t>3,1</t>
   </si>
   <si>
     <t>血量增幅</t>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -2460,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <v>1888</v>
+        <v>2888</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>96</v>
@@ -2498,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>1888</v>
+        <v>2888</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>99</v>
@@ -2536,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <v>1888</v>
+        <v>2888</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>102</v>
@@ -2571,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <v>1888</v>
+        <v>2888</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>104</v>
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="1">
-        <v>1888</v>
+        <v>2888</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>82</v>
@@ -2641,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>1888</v>
+        <v>2888</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>85</v>
@@ -2676,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="L41" s="1">
-        <v>1888</v>
+        <v>2888</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>68</v>
@@ -2711,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="L42" s="1">
-        <v>1888</v>
+        <v>2888</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>72</v>
@@ -2754,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="1">
-        <v>4888</v>
+        <v>8888</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>111</v>
@@ -2789,7 +2789,7 @@
         <v>1</v>
       </c>
       <c r="L45" s="1">
-        <v>4888</v>
+        <v>8888</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>113</v>
@@ -2824,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="1">
-        <v>4888</v>
+        <v>8888</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>115</v>
@@ -2859,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="L47" s="1">
-        <v>4888</v>
+        <v>8888</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>117</v>
@@ -2894,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="L48" s="1">
-        <v>4888</v>
+        <v>8888</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>119</v>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -1744,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>18</v>
@@ -1779,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>22</v>
@@ -1814,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>25</v>
@@ -1849,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>29</v>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>32</v>
@@ -1919,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>35</v>
@@ -1954,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>48</v>
@@ -1989,7 +1989,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>51</v>
@@ -2024,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>54</v>
@@ -2059,7 +2059,7 @@
         <v>9999</v>
       </c>
       <c r="L22" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>58</v>
@@ -2094,7 +2094,7 @@
         <v>9999</v>
       </c>
       <c r="L23" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>61</v>
@@ -2129,7 +2129,7 @@
         <v>9999</v>
       </c>
       <c r="L24" s="1">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>64</v>
@@ -2172,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="L26" s="1">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>68</v>
@@ -2207,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="L27" s="1">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>72</v>
@@ -2242,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="1">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>76</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="L29" s="1">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>79</v>
@@ -2312,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>82</v>
@@ -2347,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="1">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>85</v>
@@ -2382,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="L32" s="1">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>89</v>
@@ -2417,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="L33" s="1">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>92</v>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -338,7 +338,7 @@
     <t>宠物继承损耗-5</t>
   </si>
   <si>
-    <t>学徒铁锤</t>
+    <t>强化宝石</t>
   </si>
   <si>
     <t>强化等级上限+5</t>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -140,13 +145,13 @@
     <t>大药囊</t>
   </si>
   <si>
-    <t>10000,15</t>
+    <t>10000,10</t>
   </si>
   <si>
     <t>大铁盾</t>
   </si>
   <si>
-    <t>500,15</t>
+    <t>500,10</t>
   </si>
   <si>
     <t>大铁剑</t>
@@ -155,7 +160,7 @@
     <t>大木剑</t>
   </si>
   <si>
-    <t>1000,15</t>
+    <t>600,12</t>
   </si>
   <si>
     <t>大珍珠</t>
@@ -170,7 +175,7 @@
     <t>4,1007</t>
   </si>
   <si>
-    <t>1000,10</t>
+    <t>600,10</t>
   </si>
   <si>
     <t>物伤加成</t>
@@ -188,7 +193,7 @@
     <t>神力戒指</t>
   </si>
   <si>
-    <t>5,1009</t>
+    <t>6,1009</t>
   </si>
   <si>
     <t>道伤加成</t>
@@ -200,7 +205,7 @@
     <t>1001,2001</t>
   </si>
   <si>
-    <t>3,1</t>
+    <t>2,1</t>
   </si>
   <si>
     <t>血量增幅</t>
@@ -290,7 +295,7 @@
     <t>伤害护符</t>
   </si>
   <si>
-    <t>1007,27</t>
+    <t>1003,27</t>
   </si>
   <si>
     <t>10,10</t>
@@ -302,7 +307,7 @@
     <t>免伤护符</t>
   </si>
   <si>
-    <t>1008,28</t>
+    <t>1002,28</t>
   </si>
   <si>
     <t>伤害减免</t>
@@ -332,10 +337,10 @@
     <t>7开始，固定属性为攻击，防御，血量倍率为3%</t>
   </si>
   <si>
-    <t>秘之契约</t>
-  </si>
-  <si>
-    <t>宠物继承损耗-5</t>
+    <t>强化宝典</t>
+  </si>
+  <si>
+    <t>装备基础属性+10%</t>
   </si>
   <si>
     <t>强化宝石</t>
@@ -356,7 +361,7 @@
     <t>影魔之刃</t>
   </si>
   <si>
-    <t>技能印记</t>
+    <t>破限通玄箓</t>
   </si>
   <si>
     <t>10001,10002,10003</t>
@@ -365,28 +370,28 @@
     <t>技能词条需求-1</t>
   </si>
   <si>
-    <t>神之契约</t>
-  </si>
-  <si>
-    <t>宠物继承损耗-15</t>
-  </si>
-  <si>
-    <t>黄金兽栏</t>
+    <t>飞影追魂卷</t>
+  </si>
+  <si>
+    <t>解锁神器飞影追魂卷</t>
+  </si>
+  <si>
+    <t>万兽列阵图</t>
   </si>
   <si>
     <t>宠物备战位+1</t>
   </si>
   <si>
-    <t>驯兽金印</t>
-  </si>
-  <si>
-    <t>宠物出战位置+1</t>
-  </si>
-  <si>
-    <t>传奇铁锤</t>
-  </si>
-  <si>
-    <t>装备基础属性+50%</t>
+    <t>流光逐影印</t>
+  </si>
+  <si>
+    <t>解锁神器流光逐影印</t>
+  </si>
+  <si>
+    <t>百炼升龙锤</t>
+  </si>
+  <si>
+    <t>装备基础属性+40%</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1030,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1033,6 +1038,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1499,10 +1505,10 @@
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="1">
@@ -1534,10 +1540,10 @@
       <c r="D7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G7" s="1">
@@ -1569,10 +1575,10 @@
       <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G8" s="1">
@@ -1604,10 +1610,10 @@
       <c r="D9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="1">
@@ -1639,10 +1645,10 @@
       <c r="D10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="1">
@@ -1674,10 +1680,10 @@
       <c r="D11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="1">
@@ -1722,10 +1728,10 @@
       <c r="D13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G13" s="1">
@@ -1757,10 +1763,10 @@
       <c r="D14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>39</v>
       </c>
       <c r="G14" s="1">
@@ -1792,10 +1798,10 @@
       <c r="D15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>39</v>
       </c>
       <c r="G15" s="1">
@@ -1827,10 +1833,10 @@
       <c r="D16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G16" s="1">
@@ -1862,10 +1868,10 @@
       <c r="D17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G17" s="1">
@@ -1897,10 +1903,10 @@
       <c r="D18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G18" s="1">
@@ -1932,10 +1938,10 @@
       <c r="D19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G19" s="1">
@@ -1967,10 +1973,10 @@
       <c r="D20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G20" s="1">
@@ -2002,10 +2008,10 @@
       <c r="D21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G21" s="1">
@@ -2037,10 +2043,10 @@
       <c r="D22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G22" s="1">
@@ -2072,10 +2078,10 @@
       <c r="D23" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G23" s="1">
@@ -2107,10 +2113,10 @@
       <c r="D24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G24" s="1">
@@ -2150,10 +2156,10 @@
       <c r="D26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G26" s="1">
@@ -2185,10 +2191,10 @@
       <c r="D27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G27" s="1">
@@ -2220,10 +2226,10 @@
       <c r="D28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="7" t="s">
         <v>75</v>
       </c>
       <c r="G28" s="1">
@@ -2255,10 +2261,10 @@
       <c r="D29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G29" s="1">
@@ -2290,10 +2296,10 @@
       <c r="D30" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="7" t="s">
         <v>75</v>
       </c>
       <c r="G30" s="1">
@@ -2325,10 +2331,10 @@
       <c r="D31" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="7" t="s">
         <v>75</v>
       </c>
       <c r="G31" s="1">
@@ -2360,10 +2366,10 @@
       <c r="D32" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G32" s="1">
@@ -2395,10 +2401,10 @@
       <c r="D33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G33" s="1">
@@ -2438,10 +2444,10 @@
       <c r="D35" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="1">
@@ -2476,10 +2482,10 @@
       <c r="D36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G36" s="1">
@@ -2514,17 +2520,17 @@
       <c r="D37" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G37" s="1">
-        <v>115</v>
+        <v>20001</v>
       </c>
       <c r="H37" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
@@ -2549,10 +2555,10 @@
       <c r="D38" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G38" s="1">
@@ -2584,17 +2590,17 @@
       <c r="D39" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G39" s="1">
         <v>11</v>
       </c>
       <c r="H39" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I39" s="1">
         <v>1</v>
@@ -2619,17 +2625,17 @@
       <c r="D40" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G40" s="1">
         <v>10</v>
       </c>
       <c r="H40" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
@@ -2654,17 +2660,17 @@
       <c r="D41" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G41" s="1">
         <v>21</v>
       </c>
       <c r="H41" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41" s="1">
         <v>1</v>
@@ -2689,17 +2695,17 @@
       <c r="D42" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G42" s="1">
         <v>22</v>
       </c>
       <c r="H42" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I42" s="1">
         <v>1</v>
@@ -2729,13 +2735,13 @@
       <c r="C44" s="1">
         <v>5001</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G44" s="1">
@@ -2764,20 +2770,20 @@
       <c r="C45" s="1">
         <v>5002</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G45" s="1">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I45" s="1">
         <v>1</v>
@@ -2791,7 +2797,7 @@
       <c r="L45" s="1">
         <v>8888</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2799,13 +2805,13 @@
       <c r="C46" s="1">
         <v>5003</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G46" s="1">
@@ -2834,19 +2840,19 @@
       <c r="C47" s="1">
         <v>5004</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G47" s="2">
-        <v>112</v>
-      </c>
-      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2">
         <v>1</v>
       </c>
       <c r="I47" s="1">
@@ -2861,7 +2867,7 @@
       <c r="L47" s="1">
         <v>8888</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2869,20 +2875,20 @@
       <c r="C48" s="1">
         <v>5005</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G48" s="1">
         <v>20001</v>
       </c>
       <c r="H48" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I48" s="1">
         <v>1</v>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="149">
   <si>
     <t>#</t>
   </si>
@@ -49,6 +49,9 @@
     <t>AtrVueList</t>
   </si>
   <si>
+    <t>Tid</t>
+  </si>
+  <si>
     <t>SpeId</t>
   </si>
   <si>
@@ -319,7 +322,7 @@
     <t>2001,2002,2003</t>
   </si>
   <si>
-    <t>3,3,3</t>
+    <t>6,6,6</t>
   </si>
   <si>
     <t>精炼等级上限+5</t>
@@ -361,6 +364,48 @@
     <t>影魔之刃</t>
   </si>
   <si>
+    <t>财神福袋</t>
+  </si>
+  <si>
+    <t>金币+10%</t>
+  </si>
+  <si>
+    <t>修行笔记</t>
+  </si>
+  <si>
+    <t>经验+10%</t>
+  </si>
+  <si>
+    <t>幸运宝石</t>
+  </si>
+  <si>
+    <t>品质+5%</t>
+  </si>
+  <si>
+    <t>招财宝树</t>
+  </si>
+  <si>
+    <t>爆率+5%</t>
+  </si>
+  <si>
+    <t>流光剑诀</t>
+  </si>
+  <si>
+    <t>流光剑诀距离+1</t>
+  </si>
+  <si>
+    <t>紫电神雷</t>
+  </si>
+  <si>
+    <t>紫电神雷距离+1</t>
+  </si>
+  <si>
+    <t>破魔符咒</t>
+  </si>
+  <si>
+    <t>破魔符咒距离+1</t>
+  </si>
+  <si>
     <t>破限通玄箓</t>
   </si>
   <si>
@@ -392,6 +437,48 @@
   </si>
   <si>
     <t>装备基础属性+40%</t>
+  </si>
+  <si>
+    <t>水晶祈福链</t>
+  </si>
+  <si>
+    <t>幸运+5</t>
+  </si>
+  <si>
+    <t>噬魂修罗斧</t>
+  </si>
+  <si>
+    <t>诅咒+5</t>
+  </si>
+  <si>
+    <t>技能破限箓</t>
+  </si>
+  <si>
+    <t>全技能+3</t>
+  </si>
+  <si>
+    <t>金珠聚宝匣</t>
+  </si>
+  <si>
+    <t>金币+50%</t>
+  </si>
+  <si>
+    <t>悟道明心帖</t>
+  </si>
+  <si>
+    <t>经验+50%</t>
+  </si>
+  <si>
+    <t>造化炼宝图</t>
+  </si>
+  <si>
+    <t>品质+30%</t>
+  </si>
+  <si>
+    <t>寻宝聚运箓</t>
+  </si>
+  <si>
+    <t>爆率+30%</t>
   </si>
 </sst>
 </file>
@@ -1363,37 +1450,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O48"/>
+  <dimension ref="C1:P66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="6" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="12" width="11.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="39.25" style="1" customWidth="1"/>
-    <col min="15" max="15" width="43" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="6" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="11" max="13" width="11.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="39.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="43" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:15">
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customHeight="1" spans="3:16">
       <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:15">
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:16">
       <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1427,8 +1514,11 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1462,57 +1552,60 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:15">
+      <c r="N5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:16">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -1521,33 +1614,33 @@
         <v>0</v>
       </c>
       <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
         <v>3</v>
       </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
       <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
         <v>88</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:15">
+      <c r="O6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:16">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1556,33 +1649,33 @@
         <v>0</v>
       </c>
       <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>3</v>
       </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
       <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
         <v>88</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:15">
+      <c r="O7" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1591,33 +1684,33 @@
         <v>0</v>
       </c>
       <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
         <v>3</v>
       </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
       <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
         <v>88</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:15">
+      <c r="O8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -1626,34 +1719,35 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
         <v>3</v>
       </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
       <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
         <v>88</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G10" s="1"/>
       <c r="H10" s="1">
         <v>0</v>
       </c>
@@ -1661,34 +1755,35 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>3</v>
       </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
       <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
         <v>88</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O10" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G11" s="1"/>
       <c r="H11" s="1">
         <v>0</v>
       </c>
@@ -1696,19 +1791,22 @@
         <v>0</v>
       </c>
       <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>3</v>
       </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
       <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
         <v>88</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O11" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1719,1191 +1817,1719 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="1">
         <v>2001</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G13" s="1"/>
       <c r="H13" s="1">
         <v>0</v>
       </c>
       <c r="I13" s="1">
         <v>0</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
         <v>4</v>
       </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
       <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
         <v>288</v>
       </c>
-      <c r="N13" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="1">
         <v>2002</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="1">
         <v>0</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
         <v>4</v>
       </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
       <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
         <v>288</v>
       </c>
-      <c r="N14" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O14" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="1">
         <v>2003</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="1">
         <v>0</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
         <v>4</v>
       </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
       <c r="L15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
         <v>288</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O15" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="1">
         <v>2004</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G16" s="1"/>
       <c r="H16" s="1">
         <v>0</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
         <v>4</v>
       </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
       <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
         <v>288</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O16" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C17" s="1">
         <v>2005</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
+      <c r="G17" s="1"/>
       <c r="H17" s="1">
         <v>0</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
         <v>4</v>
       </c>
-      <c r="K17" s="1">
-        <v>1</v>
-      </c>
       <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1">
         <v>288</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C18" s="1">
         <v>2006</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G18" s="1"/>
       <c r="H18" s="1">
         <v>0</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
         <v>4</v>
       </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
       <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
         <v>288</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C19" s="1">
         <v>2007</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="G19" s="1"/>
       <c r="H19" s="1">
         <v>0</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
         <v>4</v>
       </c>
-      <c r="K19" s="1">
-        <v>1</v>
-      </c>
       <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
         <v>288</v>
       </c>
-      <c r="N19" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O19" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C20" s="1">
         <v>2008</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="G20" s="1"/>
       <c r="H20" s="1">
         <v>0</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
         <v>4</v>
       </c>
-      <c r="K20" s="1">
-        <v>1</v>
-      </c>
       <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1">
         <v>288</v>
       </c>
-      <c r="N20" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O20" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C21" s="1">
         <v>2009</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="G21" s="1"/>
       <c r="H21" s="1">
         <v>0</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
         <v>4</v>
       </c>
-      <c r="K21" s="1">
-        <v>1</v>
-      </c>
       <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
         <v>288</v>
       </c>
-      <c r="N21" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O21" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C22" s="1">
         <v>2010</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22" s="1">
+        <v>58</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
         <v>10001</v>
       </c>
-      <c r="H22" s="1">
-        <v>1</v>
-      </c>
       <c r="I22" s="1">
+        <v>2</v>
+      </c>
+      <c r="J22" s="1">
         <v>10</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="2">
         <v>4</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>9999</v>
       </c>
-      <c r="L22" s="1">
+      <c r="M22" s="1">
         <v>288</v>
       </c>
-      <c r="N22" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O22" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C23" s="1">
         <v>2011</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="1">
+        <v>58</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1">
         <v>10002</v>
       </c>
-      <c r="H23" s="1">
-        <v>1</v>
-      </c>
       <c r="I23" s="1">
+        <v>2</v>
+      </c>
+      <c r="J23" s="1">
         <v>10</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="2">
         <v>4</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>9999</v>
       </c>
-      <c r="L23" s="1">
+      <c r="M23" s="1">
         <v>288</v>
       </c>
-      <c r="N23" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O23" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="1">
         <v>2012</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24" s="1">
+        <v>58</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1">
         <v>10003</v>
       </c>
-      <c r="H24" s="1">
-        <v>1</v>
-      </c>
       <c r="I24" s="1">
+        <v>2</v>
+      </c>
+      <c r="J24" s="1">
         <v>10</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="2">
         <v>4</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>9999</v>
       </c>
-      <c r="L24" s="1">
+      <c r="M24" s="1">
         <v>288</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O24" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="1">
         <v>3001</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="G26" s="1"/>
       <c r="H26" s="1">
         <v>0</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
         <v>5</v>
       </c>
-      <c r="K26" s="1">
-        <v>1</v>
-      </c>
       <c r="L26" s="1">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1">
         <v>666</v>
       </c>
-      <c r="N26" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O26" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="1">
         <v>3002</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G27" s="1"/>
       <c r="H27" s="1">
         <v>0</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
         <v>5</v>
       </c>
-      <c r="K27" s="1">
-        <v>1</v>
-      </c>
       <c r="L27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1">
         <v>666</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O27" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="1">
         <v>3003</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G28" s="1"/>
       <c r="H28" s="1">
         <v>0</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2">
         <v>5</v>
       </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
       <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
         <v>666</v>
       </c>
-      <c r="N28" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O28" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="1">
         <v>3004</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G29" s="1"/>
       <c r="H29" s="1">
         <v>0</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2">
         <v>5</v>
       </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
       <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
         <v>666</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O29" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C30" s="1">
         <v>3005</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1">
         <v>0</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
         <v>5</v>
       </c>
-      <c r="K30" s="1">
-        <v>1</v>
-      </c>
       <c r="L30" s="1">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1">
         <v>666</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O30" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C31" s="1">
         <v>3006</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G31" s="1"/>
       <c r="H31" s="1">
         <v>0</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2">
         <v>5</v>
       </c>
-      <c r="K31" s="1">
-        <v>1</v>
-      </c>
       <c r="L31" s="1">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1">
         <v>666</v>
       </c>
-      <c r="N31" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O31" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C32" s="1">
         <v>3007</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G32" s="1"/>
       <c r="H32" s="1">
         <v>0</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
         <v>5</v>
       </c>
-      <c r="K32" s="1">
-        <v>1</v>
-      </c>
       <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
         <v>666</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O32" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C33" s="1">
         <v>3008</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G33" s="1"/>
       <c r="H33" s="1">
         <v>0</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2">
         <v>5</v>
       </c>
-      <c r="K33" s="1">
-        <v>1</v>
-      </c>
       <c r="L33" s="1">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1">
         <v>666</v>
       </c>
-      <c r="N33" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C35" s="1">
+      <c r="O33" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C37" s="1">
         <v>4001</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E35" s="8" t="s">
+      <c r="D37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="1">
+      <c r="F37" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1">
         <v>116</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I37" s="1">
         <v>5</v>
       </c>
-      <c r="I35" s="1">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2">
+      <c r="J37" s="1">
+        <v>1</v>
+      </c>
+      <c r="K37" s="2">
         <v>6</v>
       </c>
-      <c r="K35" s="1">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1">
+      <c r="L37" s="1">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
         <v>2888</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="O37" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C38" s="1">
+        <v>4002</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C36" s="1">
+      <c r="G38" s="1"/>
+      <c r="H38" s="1">
+        <v>113</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2">
+        <v>6</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1">
+        <v>2888</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C39" s="1">
+        <v>4003</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1">
+        <v>20001</v>
+      </c>
+      <c r="I39" s="1">
+        <v>10</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="2">
+        <v>6</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1">
+        <v>2888</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C40" s="1">
+        <v>4004</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1">
+        <v>117</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2">
+        <v>6</v>
+      </c>
+      <c r="L40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1">
+        <v>2888</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C41" s="1">
+        <v>4005</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1">
+        <v>11</v>
+      </c>
+      <c r="I41" s="1">
+        <v>6</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="2">
+        <v>6</v>
+      </c>
+      <c r="L41" s="1">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1">
+        <v>2888</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C42" s="1">
+        <v>4006</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1">
+        <v>10</v>
+      </c>
+      <c r="I42" s="1">
+        <v>6</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="2">
+        <v>6</v>
+      </c>
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1">
+        <v>2888</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C43" s="1">
+        <v>4007</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1">
+        <v>21</v>
+      </c>
+      <c r="I43" s="1">
+        <v>6</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2">
+        <v>6</v>
+      </c>
+      <c r="L43" s="1">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1">
+        <v>2888</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C44" s="1">
+        <v>4008</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1">
+        <v>22</v>
+      </c>
+      <c r="I44" s="1">
+        <v>30</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="2">
+        <v>6</v>
+      </c>
+      <c r="L44" s="1">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1">
+        <v>2888</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C45" s="1">
+        <v>4009</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1">
+        <v>81</v>
+      </c>
+      <c r="I45" s="1">
+        <v>10</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2">
+        <v>6</v>
+      </c>
+      <c r="L45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="1">
+        <v>2888</v>
+      </c>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C46" s="1">
+        <v>4010</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1">
+        <v>82</v>
+      </c>
+      <c r="I46" s="1">
+        <v>10</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2">
+        <v>6</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1">
+        <v>2888</v>
+      </c>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C47" s="1">
+        <v>4011</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1">
+        <v>83</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="2">
+        <v>6</v>
+      </c>
+      <c r="L47" s="1">
+        <v>1</v>
+      </c>
+      <c r="M47" s="1">
+        <v>2888</v>
+      </c>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C48" s="1">
+        <v>4012</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1">
+        <v>84</v>
+      </c>
+      <c r="I48" s="1">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="2">
+        <v>6</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1">
+        <v>2888</v>
+      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C49" s="1">
+        <v>4013</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G49" s="1">
+        <v>4001</v>
+      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="2">
+        <v>6</v>
+      </c>
+      <c r="L49" s="1">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1">
+        <v>2888</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C50" s="1">
+        <v>4014</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G50" s="1">
         <v>4002</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="7" t="s">
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="2">
+        <v>6</v>
+      </c>
+      <c r="L50" s="1">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1">
+        <v>2888</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C51" s="1">
+        <v>4015</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="G36" s="1">
-        <v>113</v>
-      </c>
-      <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2">
+      <c r="F51" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G51" s="1">
+        <v>4003</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="2">
         <v>6</v>
       </c>
-      <c r="K36" s="1">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1">
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1">
         <v>2888</v>
       </c>
-      <c r="N36" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C37" s="1">
-        <v>4003</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G37" s="1">
+      <c r="N51" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C52" s="1"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C53" s="1"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C54" s="1"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C55" s="1">
+        <v>5001</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1">
+        <v>114</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="2">
+        <v>7</v>
+      </c>
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1">
+        <v>8888</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C56" s="1">
+        <v>5002</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+      <c r="K56" s="2">
+        <v>7</v>
+      </c>
+      <c r="L56" s="1">
+        <v>1</v>
+      </c>
+      <c r="M56" s="1">
+        <v>8888</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C57" s="1">
+        <v>5003</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1">
+        <v>111</v>
+      </c>
+      <c r="I57" s="1">
+        <v>1</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+      <c r="K57" s="2">
+        <v>7</v>
+      </c>
+      <c r="L57" s="1">
+        <v>1</v>
+      </c>
+      <c r="M57" s="1">
+        <v>8888</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C58" s="1">
+        <v>5004</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2">
+        <v>1</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+      <c r="K58" s="2">
+        <v>7</v>
+      </c>
+      <c r="L58" s="1">
+        <v>1</v>
+      </c>
+      <c r="M58" s="1">
+        <v>8888</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C59" s="1">
+        <v>5005</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1">
         <v>20001</v>
       </c>
-      <c r="H37" s="1">
-        <v>10</v>
-      </c>
-      <c r="I37" s="1">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2">
-        <v>6</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1</v>
-      </c>
-      <c r="L37" s="1">
-        <v>2888</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C38" s="1">
-        <v>4004</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G38" s="1">
-        <v>117</v>
-      </c>
-      <c r="H38" s="1">
+      <c r="I59" s="1">
+        <v>40</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1</v>
+      </c>
+      <c r="K59" s="2">
+        <v>7</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+      <c r="M59" s="1">
+        <v>8888</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:15">
+      <c r="C60" s="1">
+        <v>5006</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H60" s="1">
+        <v>7</v>
+      </c>
+      <c r="I60" s="1">
         <v>5</v>
       </c>
-      <c r="I38" s="1">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2">
-        <v>6</v>
-      </c>
-      <c r="K38" s="1">
-        <v>1</v>
-      </c>
-      <c r="L38" s="1">
-        <v>2888</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C39" s="1">
-        <v>4005</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G39" s="1">
-        <v>11</v>
-      </c>
-      <c r="H39" s="1">
-        <v>6</v>
-      </c>
-      <c r="I39" s="1">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2">
-        <v>6</v>
-      </c>
-      <c r="K39" s="1">
-        <v>1</v>
-      </c>
-      <c r="L39" s="1">
-        <v>2888</v>
-      </c>
-      <c r="N39" s="2" t="s">
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="2">
+        <v>7</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:15">
+      <c r="C61" s="1">
+        <v>5007</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H61" s="1">
+        <v>8</v>
+      </c>
+      <c r="I61" s="1">
+        <v>5</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1</v>
+      </c>
+      <c r="K61" s="2">
+        <v>7</v>
+      </c>
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:15">
+      <c r="C62" s="1">
+        <v>5008</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H62" s="1">
+        <v>21000</v>
+      </c>
+      <c r="I62" s="1">
+        <v>3</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1</v>
+      </c>
+      <c r="K62" s="2">
+        <v>7</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:15">
+      <c r="C63" s="1">
+        <v>5009</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H63" s="1">
+        <v>81</v>
+      </c>
+      <c r="I63" s="1">
+        <v>50</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1</v>
+      </c>
+      <c r="K63" s="2">
+        <v>7</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:15">
+      <c r="C64" s="1">
+        <v>5010</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H64" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C40" s="1">
-        <v>4006</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G40" s="1">
-        <v>10</v>
-      </c>
-      <c r="H40" s="1">
-        <v>6</v>
-      </c>
-      <c r="I40" s="1">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2">
-        <v>6</v>
-      </c>
-      <c r="K40" s="1">
-        <v>1</v>
-      </c>
-      <c r="L40" s="1">
-        <v>2888</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C41" s="1">
-        <v>4007</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G41" s="1">
-        <v>21</v>
-      </c>
-      <c r="H41" s="1">
-        <v>6</v>
-      </c>
-      <c r="I41" s="1">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2">
-        <v>6</v>
-      </c>
-      <c r="K41" s="1">
-        <v>1</v>
-      </c>
-      <c r="L41" s="1">
-        <v>2888</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C42" s="1">
-        <v>4008</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G42" s="1">
-        <v>22</v>
-      </c>
-      <c r="H42" s="1">
+      <c r="I64" s="1">
+        <v>50</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="2">
+        <v>7</v>
+      </c>
+      <c r="L64" s="1">
+        <v>1</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:15">
+      <c r="C65" s="1">
+        <v>5011</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H65" s="1">
+        <v>83</v>
+      </c>
+      <c r="I65" s="1">
         <v>30</v>
       </c>
-      <c r="I42" s="1">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2">
-        <v>6</v>
-      </c>
-      <c r="K42" s="1">
-        <v>1</v>
-      </c>
-      <c r="L42" s="1">
-        <v>2888</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C43" s="1"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C44" s="1">
-        <v>5001</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G44" s="1">
-        <v>114</v>
-      </c>
-      <c r="H44" s="1">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2">
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="2">
         <v>7</v>
       </c>
-      <c r="K44" s="1">
-        <v>1</v>
-      </c>
-      <c r="L44" s="1">
-        <v>8888</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C45" s="1">
-        <v>5002</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1">
-        <v>1</v>
-      </c>
-      <c r="I45" s="1">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2">
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:15">
+      <c r="C66" s="1">
+        <v>5012</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H66" s="1">
+        <v>84</v>
+      </c>
+      <c r="I66" s="1">
+        <v>30</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="2">
         <v>7</v>
       </c>
-      <c r="K45" s="1">
-        <v>1</v>
-      </c>
-      <c r="L45" s="1">
-        <v>8888</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C46" s="1">
-        <v>5003</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G46" s="1">
-        <v>111</v>
-      </c>
-      <c r="H46" s="1">
-        <v>1</v>
-      </c>
-      <c r="I46" s="1">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2">
-        <v>7</v>
-      </c>
-      <c r="K46" s="1">
-        <v>1</v>
-      </c>
-      <c r="L46" s="1">
-        <v>8888</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C47" s="1">
-        <v>5004</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G47" s="2">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2">
-        <v>1</v>
-      </c>
-      <c r="I47" s="1">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2">
-        <v>7</v>
-      </c>
-      <c r="K47" s="1">
-        <v>1</v>
-      </c>
-      <c r="L47" s="1">
-        <v>8888</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C48" s="1">
-        <v>5005</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G48" s="1">
-        <v>20001</v>
-      </c>
-      <c r="H48" s="1">
-        <v>40</v>
-      </c>
-      <c r="I48" s="1">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2">
-        <v>7</v>
-      </c>
-      <c r="K48" s="1">
-        <v>1</v>
-      </c>
-      <c r="L48" s="1">
-        <v>8888</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>119</v>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -3014,7 +3014,7 @@
         <v>96</v>
       </c>
       <c r="G49" s="1">
-        <v>4001</v>
+        <v>40001</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -3048,7 +3048,7 @@
         <v>96</v>
       </c>
       <c r="G50" s="1">
-        <v>4002</v>
+        <v>40002</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -3082,7 +3082,7 @@
         <v>96</v>
       </c>
       <c r="G51" s="1">
-        <v>4003</v>
+        <v>40003</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -3336,6 +3336,9 @@
       <c r="L60" s="1">
         <v>1</v>
       </c>
+      <c r="M60" s="1">
+        <v>8888</v>
+      </c>
       <c r="O60" s="1" t="s">
         <v>136</v>
       </c>
@@ -3368,6 +3371,9 @@
       <c r="L61" s="1">
         <v>1</v>
       </c>
+      <c r="M61" s="1">
+        <v>8888</v>
+      </c>
       <c r="O61" s="1" t="s">
         <v>138</v>
       </c>
@@ -3400,6 +3406,9 @@
       <c r="L62" s="1">
         <v>1</v>
       </c>
+      <c r="M62" s="1">
+        <v>8888</v>
+      </c>
       <c r="O62" s="1" t="s">
         <v>140</v>
       </c>
@@ -3421,7 +3430,7 @@
         <v>81</v>
       </c>
       <c r="I63" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J63" s="1">
         <v>1</v>
@@ -3431,6 +3440,9 @@
       </c>
       <c r="L63" s="1">
         <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <v>8888</v>
       </c>
       <c r="O63" s="1" t="s">
         <v>142</v>
@@ -3453,7 +3465,7 @@
         <v>82</v>
       </c>
       <c r="I64" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J64" s="1">
         <v>1</v>
@@ -3463,6 +3475,9 @@
       </c>
       <c r="L64" s="1">
         <v>1</v>
+      </c>
+      <c r="M64" s="1">
+        <v>8888</v>
       </c>
       <c r="O64" s="1" t="s">
         <v>144</v>
@@ -3485,7 +3500,7 @@
         <v>83</v>
       </c>
       <c r="I65" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J65" s="1">
         <v>1</v>
@@ -3495,6 +3510,9 @@
       </c>
       <c r="L65" s="1">
         <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <v>8888</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>146</v>
@@ -3517,7 +3535,7 @@
         <v>84</v>
       </c>
       <c r="I66" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J66" s="1">
         <v>1</v>
@@ -3527,6 +3545,9 @@
       </c>
       <c r="L66" s="1">
         <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <v>8888</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>148</v>

--- a/Excel/StoreConfig.xlsx
+++ b/Excel/StoreConfig.xlsx
@@ -460,25 +460,25 @@
     <t>金珠聚宝匣</t>
   </si>
   <si>
-    <t>金币+50%</t>
+    <t>金币+100%</t>
   </si>
   <si>
     <t>悟道明心帖</t>
   </si>
   <si>
-    <t>经验+50%</t>
+    <t>经验+100%</t>
   </si>
   <si>
     <t>造化炼宝图</t>
   </si>
   <si>
-    <t>品质+30%</t>
+    <t>品质+50%</t>
   </si>
   <si>
     <t>寻宝聚运箓</t>
   </si>
   <si>
-    <t>爆率+30%</t>
+    <t>爆率+50%</t>
   </si>
 </sst>
 </file>
